--- a/ParaBankAutomationFramework/src/test/resources/testdata/ParabankData.xlsx
+++ b/ParaBankAutomationFramework/src/test/resources/testdata/ParabankData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="86">
   <si>
     <t>FirstName</t>
   </si>
@@ -236,6 +236,42 @@
   </si>
   <si>
     <t>suraj1781280594311</t>
+  </si>
+  <si>
+    <t>suraj1781288433763</t>
+  </si>
+  <si>
+    <t>suraj1781314308346</t>
+  </si>
+  <si>
+    <t>suraj1781314402787</t>
+  </si>
+  <si>
+    <t>suraj1781314978408</t>
+  </si>
+  <si>
+    <t>suraj1781315027243</t>
+  </si>
+  <si>
+    <t>suraj1781315446786</t>
+  </si>
+  <si>
+    <t>suraj1781315704819</t>
+  </si>
+  <si>
+    <t>suraj1781315803399</t>
+  </si>
+  <si>
+    <t>suraj1781316257623</t>
+  </si>
+  <si>
+    <t>suraj1781316348289</t>
+  </si>
+  <si>
+    <t>suraj1781319834740</t>
+  </si>
+  <si>
+    <t>suraj1781320156125</t>
   </si>
 </sst>
 </file>
@@ -577,7 +613,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>15</v>
